--- a/artfynd/A 58899-2023 artfynd.xlsx
+++ b/artfynd/A 58899-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58899-2023 artfynd.xlsx
+++ b/artfynd/A 58899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111880800</v>
+        <v>111880969</v>
       </c>
       <c r="B2" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590224</v>
+        <v>590321</v>
       </c>
       <c r="R2" t="n">
-        <v>6325880</v>
+        <v>6326084</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -794,66 +784,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111880865</v>
+        <v>112584823</v>
       </c>
       <c r="B3" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torp 4:6, Sm</t>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590313</v>
+        <v>590246</v>
       </c>
       <c r="R3" t="n">
-        <v>6326018</v>
+        <v>6325954</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,78 +883,61 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Lars Engström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111880789</v>
+        <v>112584810</v>
       </c>
       <c r="B4" t="n">
-        <v>96720</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Torp 4:6, Sm</t>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590212</v>
+        <v>590244</v>
       </c>
       <c r="R4" t="n">
-        <v>6325852</v>
+        <v>6325950</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -999,12 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,78 +995,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111880844</v>
+        <v>112584845</v>
       </c>
       <c r="B5" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Torp 4:6, Sm</t>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590291</v>
+        <v>590264</v>
       </c>
       <c r="R5" t="n">
-        <v>6325998</v>
+        <v>6326001</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,12 +1080,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosöksområde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,19 +1109,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Jan Brenander, Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1154,16 +1130,11 @@
         <v>113645641</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1268,16 +1239,11 @@
         <v>113645754</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1376,6 +1342,1608 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111880764</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590180</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6325836</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111880789</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590212</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6325852</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111880800</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590224</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6325880</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111880805</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>590207</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6325905</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111880844</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>590291</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6325998</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>111880865</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>590313</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6326018</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111880882</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>590311</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6326062</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>111880900</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>590320</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6326087</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111881006</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Torp 4:6, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>590342</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6326120</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112584541</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Torp 4.6, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>590230</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6325938</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112584550</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Torp 4.6, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590254</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6325975</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112584804</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>590244</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6325950</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112584886</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>590276</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6326013</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>112584797</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Torp, Boslättdammen  Mönsterås kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>590229</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6325931</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58899-2023 artfynd.xlsx
+++ b/artfynd/A 58899-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880969</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584823</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584845</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113645641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113645754</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880764</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880789</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880800</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1798,6 +1848,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880805</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2026,6 +2086,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880865</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2140,6 +2205,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880882</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2254,6 +2324,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880900</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2368,6 +2443,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111881006</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2482,6 +2562,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584541</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2596,6 +2681,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584550</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2712,6 +2802,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584804</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2828,6 +2923,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584886</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2944,8 +3044,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112584797</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>